--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  01.09.2025 a 07.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  01.09.2025 a 07.09.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE1B64E7-D4BB-45DC-ABDE-AFD2320922D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3510BA2-E1C4-405D-BE29-B8E3A542A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="128">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -343,6 +343,113 @@
   </si>
   <si>
     <t xml:space="preserve">JEFFERSON HENRIQUE DIAS SA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITOR SANTANA ALVES                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROWAY COMERCIO DE ELETRONICOS LTDA EPP      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLADIMAR FERNANDES DE JESUS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO CRISTIANO DA SILVA                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: FOTOS PENDENTES: Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO JOSE FERREIRA FILHO                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: PAINEL COM CARRO LIGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R PANTOJA RODRIGUES LTDA ME                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE LATERAL DO PASSAGEIRO E DO MOTORISTA. TRASEIRA LATERAL DO PASSAGEIRO E DO MOTORISTA. CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAPA PRESTACAO DE SERVICO LTDA ME            </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE E LATERAL DO PASSEIRO E MOTORISTA. TRASEIRA LATERAL DO PASSEIRO E DO MOTORISTA. CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME GONCALVES VIEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEBASTIAO DE SOUZA                           </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 02/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L P COMERCIO DE ALIMENTOS LTDA ME            </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEYDSON DE JESUS RODRIGUES                   </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Motor e placa, Painel com carro ligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAIN RIBEIRO                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA MESSA DA COSTA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILEUSA ALVES BALBIN                        </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE pela regra de mudança de cobertura ocorre a redução de
+uma classes de bônus, assim sendo o correto bônus  0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO GABRIEL SANTOS MOREIRA                 </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLD BRASIL SOLUCOES FINANCEIRAS LTDA ME     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITOR SOARES PEIXOTO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANO MAMPRIM                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALEB CERUTTI DA ROCHA LTDA ME               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA REIS BRITO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WESLLEN BUENO CORDEIRO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO FREIRE DE SOUZA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIANE FERNANDA DA SILVA ANDERSEN            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLODOALDO RODRIGUES PAZ                      </t>
+  </si>
+  <si>
+    <t>SAO SEBASTIAO LOCACAO DE VEICULOS E TURISMO L</t>
   </si>
 </sst>
 </file>
@@ -579,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -711,7 +818,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2484,7 +2602,7 @@
       <c r="G15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="53" t="s">
+      <c r="H15" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="27">
@@ -2513,7 +2631,7 @@
       <c r="G16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="I16" s="27">
@@ -2542,7 +2660,7 @@
       <c r="G17" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="27">
@@ -2571,7 +2689,7 @@
       <c r="G18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="I18" s="27">
@@ -2600,7 +2718,7 @@
       <c r="G19" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="H19" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="27">
@@ -2658,7 +2776,7 @@
       <c r="G21" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="H21" s="9" t="s">
         <v>79</v>
       </c>
       <c r="I21" s="27">
@@ -2687,7 +2805,7 @@
       <c r="G22" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="53" t="s">
+      <c r="H22" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I22" s="27">
@@ -2716,7 +2834,7 @@
       <c r="G23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H23" s="53" t="s">
+      <c r="H23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="I23" s="27">
@@ -2745,7 +2863,7 @@
       <c r="G24" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="53" t="s">
+      <c r="H24" s="9" t="s">
         <v>84</v>
       </c>
       <c r="I24" s="27">
@@ -2977,7 +3095,7 @@
       <c r="G32" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H32" s="53" t="s">
+      <c r="H32" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="27">
@@ -3247,7 +3365,7 @@
     <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
     <col min="9" max="9" width="21" style="27" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3284,303 +3402,767 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="55">
+        <v>45891</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D2" s="25">
+        <v>134079742</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450061626</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="55">
+        <v>45896</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D3" s="25">
+        <v>134145131</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450065290</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="55">
+        <v>45899</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D4" s="25">
+        <v>134160503</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450065058</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="55">
+        <v>45895</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D5" s="25">
+        <v>134131446</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450064695</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="55">
+        <v>45897</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D6" s="25">
+        <v>134167984</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450066598</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="55">
+        <v>45897</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D7" s="25">
+        <v>134179873</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450067390</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="55">
+        <v>45896</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D8" s="25">
+        <v>134147122</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450065510</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="55">
+        <v>45900</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D9" s="25">
+        <v>134214197</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450069117</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45900</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="55">
+        <v>45910</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D10" s="25">
+        <v>134238726</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450070008</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45902</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="55">
+        <v>45909</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D11" s="25">
+        <v>134059342</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450060647</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="55">
+        <v>45895</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D12" s="25">
+        <v>134116242</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450063584</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="55">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D13" s="25">
+        <v>134081030</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450061681</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="55">
+        <v>45910</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D14" s="25">
+        <v>134148746</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450065652</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="55">
+        <v>45890</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D15" s="25">
+        <v>134053193</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450060230</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45899</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="B16" s="55">
+        <v>45895</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D16" s="25">
+        <v>134123155</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450064101</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D17" s="25">
+        <v>134079280</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450061593</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45902</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D18" s="25">
+        <v>134263582</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450071724</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45901</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D19" s="25">
+        <v>134242353</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450069777</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D20" s="25">
+        <v>134064264</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450060780</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D21" s="25">
+        <v>134068199</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450060933</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D22" s="25">
+        <v>134073616</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450061330</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D23" s="25">
+        <v>134074618</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450061351</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D24" s="25">
+        <v>134075021</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450061362</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D25" s="25">
+        <v>134076325</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450061428</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D26" s="25">
+        <v>134179739</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450067380</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45903</v>
+      </c>
+      <c r="D27" s="25">
+        <v>134177114</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450067170</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="20"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="28"/>
@@ -3590,7 +4172,7 @@
       <c r="G29" s="24"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="28"/>
@@ -3600,7 +4182,7 @@
       <c r="G30" s="24"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="28"/>
@@ -3610,7 +4192,7 @@
       <c r="G31" s="24"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="28"/>
@@ -3732,18 +4314,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A28:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A27 A2:B16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6351,49 +6933,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496573</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496573</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496573</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6402,7 +6941,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6452,9 +6991,9 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6492,6 +7031,7 @@
                 <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns3:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6724,6 +7264,11 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="39" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
     <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
@@ -6824,18 +7369,61 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496573</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496573</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496573</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3965E57E-4F4E-44C0-B021-D89F8EC97D7C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098F1F3C-7054-44DA-97C1-1FA0AD811FFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  01.09.2025 a 07.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  01.09.2025 a 07.09.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3510BA2-E1C4-405D-BE29-B8E3A542A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F4CF795-C20F-4EC4-AF28-4E26D87CCB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="193">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -450,6 +450,212 @@
   </si>
   <si>
     <t>SAO SEBASTIAO LOCACAO DE VEICULOS E TURISMO L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS LUAN NEVES SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEIDE FERREIRA DE DEUS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARDEL VIEIRA GOMES 71532790406              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANZ WILLI VAN WELL                         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGELA MARIA DOS REIS                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO JORGE SIMAO DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANO PONTALTI MARCONDES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCA VANIA CARNEIRO PASSOS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE EMANUEL GONCALVES PEREIRA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Motor e placa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIANE CABRAL CARVALHO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLAN ROBERTO DE CASTRO VIRGENS              </t>
+  </si>
+  <si>
+    <t>REAL LEVARE LOCADORA FRETAMENTO E TURISMO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANAINA NABERCE BEZERRA                      </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL DE BRITO                              </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do motorista, Traseira e lateral do passageiro, Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS CONSTRUTORA LTDA ME                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIZELE ALVES DA COSTA                        </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 03.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELENO ALVES RIBEIRO NETO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGOR MARTINS ESTEVAO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA KRUGER REHN                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) CAMILA KRUGER REHN, pois este consta como condutor a menos de
+60 dias na apólice.&lt;br&gt;Para que possamos seguir com a emissão do d
+ocumento, a forma de contratação deverá ocorrer como Seguro Novo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL BARBOSA MENEZES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS MARCELO LOPES RIBEIRO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBENS APARECIDO DA COSTA                    </t>
+  </si>
+  <si>
+    <t>Informamos que o veículo da proposta em questão se encontra em dup
+licidade com uma apólice de outra corretagem, para prosseguirmos c
+om a emissão se faz necessário realizar o cancelamento da mesma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ANTONIO EHNKE                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro, Frente e lateral do motorista, Motor e placa, Porta malas aberto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA PRISCILLA CARANA RABESCO MARCONDES     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIA LUCENA GONCALVES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUEL RAMALHO SALES DE SOUZA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS CARLOS CASTELANI                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CRISTINA DE OLIVEIRA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILENE GOMES TELLES                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUSTAVO PROCESSY DE FREITAS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCA DE PAULA CARVALHO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS SANTOS SOUZA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUARDO DE SOUZA                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISMAEL AMARAL DE JESUS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIO OMAR GARCIA                            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CICERO JOSE DE MORAIS PIRES                  </t>
+  </si>
+  <si>
+    <t>F
+avor enviar cópia completa da apólice anterior 2024/2025 (atual) a
+través desse e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEAYTON VIEIRA DOS SANTOS JUNIOR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILDAZIO BATISTA DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAREN DE SOUZA COUTO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDEMIR BARTOLOMEU                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA DE FATIMA OLIVEIRA CORREA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENAN WILLIAM PONCIO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS AUGUSTO DE BARROS GREGORIO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON GOMES DE ALMEIDA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRIAM KEILA BARCELLOS COIMBRA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA KROHLING                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERARIS AMARO SILVA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO JOSE DO NASCIMENTO LTDA ME             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO VITOR DA SILVA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO BATISTA DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO GONCALVES DA CUNHA ME                  </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI ( FOTO COM BAIXA ILUMINAÇÃO / IMPOSSIBILIDADE DE LEITURA DA FOTO DO CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELI DO PRADO MACEDO                        </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: DOCUMENTO DO VEICULO. TRASEIRA LATERAL DO MOTORISTA.</t>
   </si>
 </sst>
 </file>
@@ -686,7 +892,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -758,9 +964,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -827,9 +1030,30 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1255,13 +1479,13 @@
       <c r="C3" s="7">
         <v>45901</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="45" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="18">
         <v>3450068292</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -1285,7 +1509,7 @@
       <c r="D4" s="25">
         <v>134003210</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="47">
         <v>3450057655</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1314,7 +1538,7 @@
       <c r="D5" s="25">
         <v>134099220</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="47">
         <v>3450062594</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -1343,7 +1567,7 @@
       <c r="D6" s="25">
         <v>134133670</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="47">
         <v>3450064915</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1372,7 +1596,7 @@
       <c r="D7" s="25">
         <v>134122888</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="47">
         <v>3450064068</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1401,7 +1625,7 @@
       <c r="D8" s="25">
         <v>134159622</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="47">
         <v>3450063408</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1430,7 +1654,7 @@
       <c r="D9" s="25">
         <v>134150286</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="47">
         <v>3450065730</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1459,7 +1683,7 @@
       <c r="D10" s="25">
         <v>134207612</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="47">
         <v>3450068908</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1488,7 +1712,7 @@
       <c r="D11" s="25">
         <v>134208212</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="47">
         <v>3450068963</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1517,7 +1741,7 @@
       <c r="D12" s="25">
         <v>134169985</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="47">
         <v>3450066686</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1546,7 +1770,7 @@
       <c r="D13" s="25">
         <v>134188708</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="47">
         <v>3450067753</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1575,7 +1799,7 @@
       <c r="D14" s="25">
         <v>134102658</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="47">
         <v>3450062869</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1604,7 +1828,7 @@
       <c r="D15" s="25">
         <v>134175235</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="47">
         <v>3450067050</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1633,7 +1857,7 @@
       <c r="D16" s="25">
         <v>134128924</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="47">
         <v>3450064464</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1662,7 +1886,7 @@
       <c r="D17" s="25">
         <v>134084701</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="47">
         <v>3450062033</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1691,7 +1915,7 @@
       <c r="D18" s="25">
         <v>134130675</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="47">
         <v>3450064630</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1720,7 +1944,7 @@
       <c r="D19" s="25">
         <v>134077451</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="47">
         <v>3450061494</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1749,7 +1973,7 @@
       <c r="D20" s="25">
         <v>134013561</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="47">
         <v>3450058425</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -1769,9 +1993,9 @@
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="47"/>
+      <c r="D21" s="46"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="49"/>
+      <c r="F21" s="48"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
@@ -2225,7 +2449,7 @@
       <c r="E2" s="18">
         <v>3450069238</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -2273,13 +2497,13 @@
       <c r="C4" s="7">
         <v>45902</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="50">
         <v>3450069546</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="30" t="s">
         <v>54</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -2367,10 +2591,10 @@
       <c r="F7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="30" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="27">
@@ -3394,7 +3618,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3402,7 +3626,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="55">
+      <c r="B2" s="54">
         <v>45891</v>
       </c>
       <c r="C2" s="28">
@@ -3431,7 +3655,7 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>45896</v>
       </c>
       <c r="C3" s="28">
@@ -3449,7 +3673,7 @@
       <c r="G3" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="12" t="s">
         <v>95</v>
       </c>
       <c r="I3" s="27">
@@ -3460,7 +3684,7 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="54">
         <v>45899</v>
       </c>
       <c r="C4" s="28">
@@ -3489,7 +3713,7 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>45895</v>
       </c>
       <c r="C5" s="28">
@@ -3507,7 +3731,7 @@
       <c r="G5" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="15" t="s">
         <v>98</v>
       </c>
       <c r="I5" s="27">
@@ -3518,7 +3742,7 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="55">
+      <c r="B6" s="54">
         <v>45897</v>
       </c>
       <c r="C6" s="28">
@@ -3536,7 +3760,7 @@
       <c r="G6" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I6" s="27">
@@ -3547,7 +3771,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="54">
         <v>45897</v>
       </c>
       <c r="C7" s="28">
@@ -3565,7 +3789,7 @@
       <c r="G7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="57" t="s">
+      <c r="H7" s="9" t="s">
         <v>102</v>
       </c>
       <c r="I7" s="27">
@@ -3576,7 +3800,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="54">
         <v>45896</v>
       </c>
       <c r="C8" s="28">
@@ -3594,7 +3818,7 @@
       <c r="G8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="57" t="s">
+      <c r="H8" s="9" t="s">
         <v>104</v>
       </c>
       <c r="I8" s="27">
@@ -3605,7 +3829,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="54">
         <v>45900</v>
       </c>
       <c r="C9" s="28">
@@ -3623,7 +3847,7 @@
       <c r="G9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="27">
@@ -3634,7 +3858,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="55">
+      <c r="B10" s="54">
         <v>45910</v>
       </c>
       <c r="C10" s="28">
@@ -3652,7 +3876,7 @@
       <c r="G10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="57" t="s">
+      <c r="H10" s="9" t="s">
         <v>107</v>
       </c>
       <c r="I10" s="27">
@@ -3663,7 +3887,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="55">
+      <c r="B11" s="54">
         <v>45909</v>
       </c>
       <c r="C11" s="28">
@@ -3681,7 +3905,7 @@
       <c r="G11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="57" t="s">
+      <c r="H11" s="9" t="s">
         <v>109</v>
       </c>
       <c r="I11" s="27">
@@ -3692,7 +3916,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="55">
+      <c r="B12" s="54">
         <v>45895</v>
       </c>
       <c r="C12" s="28">
@@ -3710,7 +3934,7 @@
       <c r="G12" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="57" t="s">
+      <c r="H12" s="9" t="s">
         <v>111</v>
       </c>
       <c r="I12" s="27">
@@ -3721,7 +3945,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="55">
+      <c r="B13" s="54">
         <v>45891</v>
       </c>
       <c r="C13" s="28">
@@ -3750,7 +3974,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="55">
+      <c r="B14" s="54">
         <v>45910</v>
       </c>
       <c r="C14" s="28">
@@ -3779,7 +4003,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="55">
+      <c r="B15" s="54">
         <v>45890</v>
       </c>
       <c r="C15" s="28">
@@ -3797,7 +4021,7 @@
       <c r="G15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="57" t="s">
+      <c r="H15" s="9" t="s">
         <v>115</v>
       </c>
       <c r="I15" s="27">
@@ -3808,7 +4032,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="55">
+      <c r="B16" s="54">
         <v>45895</v>
       </c>
       <c r="C16" s="28">
@@ -3826,7 +4050,7 @@
       <c r="G16" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="57" t="s">
+      <c r="H16" s="9" t="s">
         <v>117</v>
       </c>
       <c r="I16" s="27">
@@ -3855,7 +4079,7 @@
       <c r="G17" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="9" t="s">
         <v>107</v>
       </c>
       <c r="I17" s="27">
@@ -3913,7 +4137,7 @@
       <c r="G19" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="57" t="s">
+      <c r="H19" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="27">
@@ -4145,7 +4369,7 @@
       <c r="G27" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="27">
@@ -4156,9 +4380,9 @@
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="28"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="35"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="20"/>
       <c r="H28" s="9"/>
     </row>
@@ -4335,17 +4559,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4368,7 +4592,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="62" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -4379,603 +4603,1553 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="A2" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D2" s="58">
+        <v>134129134</v>
+      </c>
+      <c r="E2" s="59">
+        <v>3450064486</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="7">
+        <v>45895</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D3" s="58">
+        <v>134117963</v>
+      </c>
+      <c r="E3" s="59">
+        <v>3450063650</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D4" s="58">
+        <v>134129842</v>
+      </c>
+      <c r="E4" s="59">
+        <v>3450064552</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D5" s="58">
+        <v>134159242</v>
+      </c>
+      <c r="E5" s="59">
+        <v>3450061098</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D6" s="58">
+        <v>134122740</v>
+      </c>
+      <c r="E6" s="59">
+        <v>3450064035</v>
+      </c>
+      <c r="F6" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D7" s="58">
+        <v>134159592</v>
+      </c>
+      <c r="E7" s="59">
+        <v>3450063485</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D8" s="58">
+        <v>134151508</v>
+      </c>
+      <c r="E8" s="59">
+        <v>3450065872</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D9" s="58">
+        <v>134151675</v>
+      </c>
+      <c r="E9" s="59">
+        <v>3450065938</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D10" s="58">
+        <v>134156726</v>
+      </c>
+      <c r="E10" s="59">
+        <v>3450066180</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D11" s="58">
+        <v>134151502</v>
+      </c>
+      <c r="E11" s="59">
+        <v>3450065861</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D12" s="58">
+        <v>134160229</v>
+      </c>
+      <c r="E12" s="59">
+        <v>3450062946</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D13" s="58">
+        <v>134142314</v>
+      </c>
+      <c r="E13" s="59">
+        <v>3450065179</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B14" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D14" s="58">
+        <v>134160191</v>
+      </c>
+      <c r="E14" s="59">
+        <v>3450062980</v>
+      </c>
+      <c r="F14" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="61" customFormat="1">
+      <c r="A15" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D15" s="57">
+        <v>134160582</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450064783</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D16" s="58">
+        <v>134158678</v>
+      </c>
+      <c r="E16" s="59">
+        <v>3450061824</v>
+      </c>
+      <c r="F16" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D17" s="58">
+        <v>134159195</v>
+      </c>
+      <c r="E17" s="59">
+        <v>3450066301</v>
+      </c>
+      <c r="F17" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45902</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D18" s="58">
+        <v>134195795</v>
+      </c>
+      <c r="E18" s="59">
+        <v>3450068138</v>
+      </c>
+      <c r="F18" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D19" s="58">
+        <v>134131938</v>
+      </c>
+      <c r="E19" s="59">
+        <v>3450064740</v>
+      </c>
+      <c r="F19" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D20" s="58">
+        <v>134151203</v>
+      </c>
+      <c r="E20" s="59">
+        <v>3450065817</v>
+      </c>
+      <c r="F20" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D21" s="58">
+        <v>134181258</v>
+      </c>
+      <c r="E21" s="59">
+        <v>3450067511</v>
+      </c>
+      <c r="F21" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45902</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D22" s="58">
+        <v>134158894</v>
+      </c>
+      <c r="E22" s="59">
+        <v>3450066268</v>
+      </c>
+      <c r="F22" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D23" s="58">
+        <v>134272282</v>
+      </c>
+      <c r="E23" s="59">
+        <v>3450072428</v>
+      </c>
+      <c r="F23" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D24" s="58">
+        <v>134073511</v>
+      </c>
+      <c r="E24" s="59">
+        <v>3450061329</v>
+      </c>
+      <c r="F24" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D25" s="58">
+        <v>134117765</v>
+      </c>
+      <c r="E25" s="59">
+        <v>3450063639</v>
+      </c>
+      <c r="F25" s="56" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D26" s="58">
+        <v>134119034</v>
+      </c>
+      <c r="E26" s="59">
+        <v>3450063727</v>
+      </c>
+      <c r="F26" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D27" s="58">
+        <v>134119881</v>
+      </c>
+      <c r="E27" s="59">
+        <v>3450063782</v>
+      </c>
+      <c r="F27" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D28" s="58">
+        <v>134123847</v>
+      </c>
+      <c r="E28" s="59">
+        <v>3450064156</v>
+      </c>
+      <c r="F28" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D29" s="58">
+        <v>134125124</v>
+      </c>
+      <c r="E29" s="59">
+        <v>3450064233</v>
+      </c>
+      <c r="F29" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D30" s="58">
+        <v>134125486</v>
+      </c>
+      <c r="E30" s="59">
+        <v>3450064255</v>
+      </c>
+      <c r="F30" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D31" s="58">
+        <v>134130794</v>
+      </c>
+      <c r="E31" s="59">
+        <v>3450064651</v>
+      </c>
+      <c r="F31" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="G31" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C32" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D32" s="58">
+        <v>134131237</v>
+      </c>
+      <c r="E32" s="59">
+        <v>3450064684</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C33" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D33" s="58">
+        <v>134133609</v>
+      </c>
+      <c r="E33" s="59">
+        <v>3450064893</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I33" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C34" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D34" s="58">
+        <v>134134215</v>
+      </c>
+      <c r="E34" s="59">
+        <v>3450064960</v>
+      </c>
+      <c r="F34" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="G34" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C35" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D35" s="58">
+        <v>134134268</v>
+      </c>
+      <c r="E35" s="59">
+        <v>3450064970</v>
+      </c>
+      <c r="F35" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C36" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D36" s="58">
+        <v>134071048</v>
+      </c>
+      <c r="E36" s="59">
+        <v>3450061109</v>
+      </c>
+      <c r="F36" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="I36" s="27">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>45900</v>
+      </c>
+      <c r="C37" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D37" s="58">
+        <v>134077361</v>
+      </c>
+      <c r="E37" s="59">
+        <v>3450061472</v>
+      </c>
+      <c r="F37" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="I37" s="27">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45921</v>
+      </c>
+      <c r="C38" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D38" s="58">
+        <v>134077137</v>
+      </c>
+      <c r="E38" s="59">
+        <v>3450061461</v>
+      </c>
+      <c r="F38" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="I38" s="27">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45902</v>
+      </c>
+      <c r="C39" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D39" s="58">
+        <v>134285315</v>
+      </c>
+      <c r="E39" s="59">
+        <v>3450070360</v>
+      </c>
+      <c r="F39" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="G39" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="27">
+        <v>45902</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C40" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D40" s="58">
+        <v>134139465</v>
+      </c>
+      <c r="E40" s="59">
+        <v>3450065091</v>
+      </c>
+      <c r="F40" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C41" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D41" s="58">
+        <v>134144563</v>
+      </c>
+      <c r="E41" s="59">
+        <v>3450065256</v>
+      </c>
+      <c r="F41" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C42" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D42" s="58">
+        <v>134146490</v>
+      </c>
+      <c r="E42" s="59">
+        <v>3450065410</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="G42" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C43" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D43" s="58">
+        <v>134146948</v>
+      </c>
+      <c r="E43" s="59">
+        <v>3450065465</v>
+      </c>
+      <c r="F43" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I43" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C44" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D44" s="58">
+        <v>134151477</v>
+      </c>
+      <c r="E44" s="59">
+        <v>3450065840</v>
+      </c>
+      <c r="F44" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="G44" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I44" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C45" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D45" s="58">
+        <v>134151955</v>
+      </c>
+      <c r="E45" s="59">
+        <v>3450065950</v>
+      </c>
+      <c r="F45" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="G45" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I45" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C46" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D46" s="58">
+        <v>134154522</v>
+      </c>
+      <c r="E46" s="59">
+        <v>3450066059</v>
+      </c>
+      <c r="F46" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="G46" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I46" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C47" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D47" s="58">
+        <v>134084614</v>
+      </c>
+      <c r="E47" s="59">
+        <v>3450062011</v>
+      </c>
+      <c r="F47" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="G47" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="I47" s="27">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C48" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D48" s="58">
+        <v>134156516</v>
+      </c>
+      <c r="E48" s="59">
+        <v>3450062088</v>
+      </c>
+      <c r="F48" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I48" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C49" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D49" s="58">
+        <v>134156704</v>
+      </c>
+      <c r="E49" s="59">
+        <v>3450062055</v>
+      </c>
+      <c r="F49" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="G49" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I49" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C50" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D50" s="58">
+        <v>134157147</v>
+      </c>
+      <c r="E50" s="59">
+        <v>3450066191</v>
+      </c>
+      <c r="F50" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="G50" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I50" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C51" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D51" s="58">
+        <v>134158807</v>
+      </c>
+      <c r="E51" s="59">
+        <v>3450061747</v>
+      </c>
+      <c r="F51" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="G51" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I51" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C52" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D52" s="58">
+        <v>134158935</v>
+      </c>
+      <c r="E52" s="59">
+        <v>3450061527</v>
+      </c>
+      <c r="F52" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I52" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C53" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D53" s="58">
+        <v>134162394</v>
+      </c>
+      <c r="E53" s="59">
+        <v>3450066323</v>
+      </c>
+      <c r="F53" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="27">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C54" s="28">
+        <v>45904</v>
+      </c>
+      <c r="D54" s="58">
+        <v>134199244</v>
+      </c>
+      <c r="E54" s="59">
+        <v>3450068370</v>
+      </c>
+      <c r="F54" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="H54" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="I54" s="27">
+        <v>45898</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A54" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G54" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5021,7 +6195,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5037,8 +6211,8 @@
       <c r="D2" s="25"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="37"/>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
@@ -5050,8 +6224,8 @@
       <c r="D3" s="25"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="37"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
@@ -5063,8 +6237,8 @@
       <c r="D4" s="25"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9">
@@ -5076,8 +6250,8 @@
       <c r="D5" s="25"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="38"/>
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9">
@@ -5089,8 +6263,8 @@
       <c r="D6" s="25"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39"/>
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9">
@@ -5102,8 +6276,8 @@
       <c r="D7" s="25"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="39"/>
       <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9">
@@ -5115,8 +6289,8 @@
       <c r="D8" s="25"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
@@ -5128,8 +6302,8 @@
       <c r="D9" s="25"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
@@ -5141,8 +6315,8 @@
       <c r="D10" s="25"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
@@ -5154,8 +6328,8 @@
       <c r="D11" s="25"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
@@ -5167,8 +6341,8 @@
       <c r="D12" s="25"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
@@ -5180,8 +6354,8 @@
       <c r="D13" s="25"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
@@ -5193,8 +6367,8 @@
       <c r="D14" s="25"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
@@ -5206,8 +6380,8 @@
       <c r="D15" s="25"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9">
@@ -5219,12 +6393,12 @@
       <c r="D16" s="25"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="29" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
@@ -5232,8 +6406,8 @@
       <c r="D17" s="25"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
@@ -5245,8 +6419,8 @@
       <c r="D18" s="25"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
@@ -5254,9 +6428,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="23"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="9"/>
       <c r="I19" s="27"/>
     </row>
@@ -5267,7 +6441,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="32"/>
       <c r="H20" s="9"/>
       <c r="I20" s="27"/>
     </row>
@@ -5278,7 +6452,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
     </row>
@@ -5289,7 +6463,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="32"/>
       <c r="H22" s="9"/>
       <c r="I22" s="27"/>
     </row>
@@ -5300,7 +6474,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="9"/>
       <c r="I23" s="27"/>
     </row>
@@ -5311,7 +6485,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="9"/>
       <c r="I24" s="27"/>
     </row>
@@ -5742,7 +6916,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -5775,8 +6949,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="23"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="27"/>
@@ -6933,65 +8107,49 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496573</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496573</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496573</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7369,61 +8527,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496573</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496573</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496573</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3965E57E-4F4E-44C0-B021-D89F8EC97D7C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3965E57E-4F4E-44C0-B021-D89F8EC97D7C}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  01.09.2025 a 07.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  01.09.2025 a 07.09.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F4CF795-C20F-4EC4-AF28-4E26D87CCB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70712B65-A1F5-46B7-B359-8EAE0EF30482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="236">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -656,6 +656,146 @@
   </si>
   <si>
     <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: DOCUMENTO DO VEICULO. TRASEIRA LATERAL DO MOTORISTA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICK BENEVIDES COSTA                      </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 04/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINICIUS FAICAL SAID                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON LUIZ DOS SANTOS MARQUES            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO DE ABREU                             </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: MOTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFERSON GUEDES SANTOS                       </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Número do Chassi, Painel com a motocicleta ligada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO DE OLIVEIRA LUJAN                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS VINICIUS DE SOUZA PARDIM ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WENDEL VENTURINO                             </t>
+  </si>
+  <si>
+    <t>NUP CANCELAMENTO 04/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUGO DA SILVA DAL PONT                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) HUGO DA SILVA DAL PONT, pois este não consta como condutor na ap
+ólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEBASTIAO SOARES DOS SANTOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMADO ANTONIO DE SENE                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE FERREIRA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO VIANA                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDA DE ARAUJO                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) FERNANDA DE ARAUJO, pois esta não consta como condutor na apólic
+eanterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA GONCALVES FRAGA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REINALDO BARBOSA LIMA                        </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Painel com a motocicleta ligada FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTA MEDINA BERINI                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRA MARIA ALVES DA SILVA                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: Motor e placa, Painel com carro ligado, Chassi, Porta malas aberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO REIS MAIA                           </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: Fotos que tiveram repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMERSON CARVALHO DA COSTA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE SOARES DE REZENDE                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILIPPE ESTRELLA FARIAS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNEI APARECIDO SERON ME                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NELSON JORGE DE LIMA FILHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAROLINA D AMORE SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA VIVAS                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO SANDERSON SILVA DE ARAUJO            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANILDO CORREIA DE MELO                      </t>
+  </si>
+  <si>
+    <t>Constatamos que o modelo do veículo informado na cotação difere do
+constado, segue abaixo as opções cadastradas pelo sistema através
+do chassi do veículo&lt;br&gt;&lt;br&gt;Modelo constatado STRADA ENDURANCE 1.
+3 FLEX8V CS 2P.&lt;br&gt;FIPE 001569-5&lt;br&gt;Valor do prêmio 10X R$ 276,53&lt;
+br&gt;Franquia R$ 4.360,48&lt;br&gt;&lt;br&gt;Gentileza nos retornar com o modelo
+correto e o de acordo para o novo prêmio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSENEY SANTOS SOUZA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILENE FLORIO BONOTO VIAL                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOCELIA PEREIRA DE SOUSA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETICIA VIEIRA ROMAO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TODAS AS FOTOS FEITAS ERRADAS, SEM PRAZO DE REENVIO.</t>
   </si>
 </sst>
 </file>
@@ -714,7 +854,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -887,12 +1027,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -978,12 +1127,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1030,21 +1174,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1054,6 +1189,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1479,7 +1636,7 @@
       <c r="C3" s="7">
         <v>45901</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="42" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="18">
@@ -1509,7 +1666,7 @@
       <c r="D4" s="25">
         <v>134003210</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="44">
         <v>3450057655</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1538,7 +1695,7 @@
       <c r="D5" s="25">
         <v>134099220</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="44">
         <v>3450062594</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -1567,7 +1724,7 @@
       <c r="D6" s="25">
         <v>134133670</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="44">
         <v>3450064915</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1596,7 +1753,7 @@
       <c r="D7" s="25">
         <v>134122888</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="44">
         <v>3450064068</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1625,7 +1782,7 @@
       <c r="D8" s="25">
         <v>134159622</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="44">
         <v>3450063408</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1654,7 +1811,7 @@
       <c r="D9" s="25">
         <v>134150286</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="44">
         <v>3450065730</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1683,7 +1840,7 @@
       <c r="D10" s="25">
         <v>134207612</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="44">
         <v>3450068908</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1712,7 +1869,7 @@
       <c r="D11" s="25">
         <v>134208212</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="44">
         <v>3450068963</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1741,7 +1898,7 @@
       <c r="D12" s="25">
         <v>134169985</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="44">
         <v>3450066686</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1770,7 +1927,7 @@
       <c r="D13" s="25">
         <v>134188708</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="44">
         <v>3450067753</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1799,7 +1956,7 @@
       <c r="D14" s="25">
         <v>134102658</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="44">
         <v>3450062869</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1828,7 +1985,7 @@
       <c r="D15" s="25">
         <v>134175235</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="44">
         <v>3450067050</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1857,7 +2014,7 @@
       <c r="D16" s="25">
         <v>134128924</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="44">
         <v>3450064464</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1886,7 +2043,7 @@
       <c r="D17" s="25">
         <v>134084701</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="44">
         <v>3450062033</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1915,7 +2072,7 @@
       <c r="D18" s="25">
         <v>134130675</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="44">
         <v>3450064630</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1944,7 +2101,7 @@
       <c r="D19" s="25">
         <v>134077451</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="44">
         <v>3450061494</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1973,7 +2130,7 @@
       <c r="D20" s="25">
         <v>134013561</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="44">
         <v>3450058425</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -1993,9 +2150,9 @@
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="46"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="48"/>
+      <c r="F21" s="45"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
@@ -2449,7 +2606,7 @@
       <c r="E2" s="18">
         <v>3450069238</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="46" t="s">
         <v>49</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -2497,10 +2654,10 @@
       <c r="C4" s="7">
         <v>45902</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="47">
         <v>3450069546</v>
       </c>
       <c r="F4" s="30" t="s">
@@ -2591,7 +2748,7 @@
       <c r="F7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="48" t="s">
         <v>40</v>
       </c>
       <c r="H7" s="30" t="s">
@@ -3626,7 +3783,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="54">
+      <c r="B2" s="51">
         <v>45891</v>
       </c>
       <c r="C2" s="28">
@@ -3655,7 +3812,7 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="51">
         <v>45896</v>
       </c>
       <c r="C3" s="28">
@@ -3684,7 +3841,7 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="51">
         <v>45899</v>
       </c>
       <c r="C4" s="28">
@@ -3713,7 +3870,7 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="51">
         <v>45895</v>
       </c>
       <c r="C5" s="28">
@@ -3742,7 +3899,7 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="51">
         <v>45897</v>
       </c>
       <c r="C6" s="28">
@@ -3771,7 +3928,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="54">
+      <c r="B7" s="51">
         <v>45897</v>
       </c>
       <c r="C7" s="28">
@@ -3800,7 +3957,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="51">
         <v>45896</v>
       </c>
       <c r="C8" s="28">
@@ -3829,7 +3986,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="51">
         <v>45900</v>
       </c>
       <c r="C9" s="28">
@@ -3858,7 +4015,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="54">
+      <c r="B10" s="51">
         <v>45910</v>
       </c>
       <c r="C10" s="28">
@@ -3887,7 +4044,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="51">
         <v>45909</v>
       </c>
       <c r="C11" s="28">
@@ -3916,7 +4073,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="51">
         <v>45895</v>
       </c>
       <c r="C12" s="28">
@@ -3945,7 +4102,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="51">
         <v>45891</v>
       </c>
       <c r="C13" s="28">
@@ -3974,7 +4131,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="51">
         <v>45910</v>
       </c>
       <c r="C14" s="28">
@@ -4003,7 +4160,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="51">
         <v>45890</v>
       </c>
       <c r="C15" s="28">
@@ -4032,7 +4189,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="51">
         <v>45895</v>
       </c>
       <c r="C16" s="28">
@@ -4380,8 +4537,8 @@
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="28"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="53"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="50"/>
       <c r="F28" s="34"/>
       <c r="G28" s="20"/>
       <c r="H28" s="9"/>
@@ -4568,7 +4725,7 @@
     <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.7109375" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -4592,7 +4749,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -4612,16 +4769,16 @@
       <c r="C2" s="28">
         <v>45904</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="52">
         <v>134129134</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="53">
         <v>3450064486</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="63" t="s">
+      <c r="G2" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H2" s="9" t="s">
@@ -4641,16 +4798,16 @@
       <c r="C3" s="28">
         <v>45904</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="52">
         <v>134117963</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="53">
         <v>3450063650</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -4670,16 +4827,16 @@
       <c r="C4" s="28">
         <v>45904</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="52">
         <v>134129842</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="53">
         <v>3450064552</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="63" t="s">
+      <c r="G4" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H4" s="9" t="s">
@@ -4699,19 +4856,19 @@
       <c r="C5" s="28">
         <v>45904</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="52">
         <v>134159242</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="53">
         <v>3450061098</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="60" t="s">
+      <c r="H5" s="9" t="s">
         <v>132</v>
       </c>
       <c r="I5" s="27">
@@ -4728,16 +4885,16 @@
       <c r="C6" s="28">
         <v>45904</v>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="52">
         <v>134122740</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="53">
         <v>3450064035</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -4757,16 +4914,16 @@
       <c r="C7" s="28">
         <v>45904</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="52">
         <v>134159592</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="53">
         <v>3450063485</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H7" s="9" t="s">
@@ -4786,16 +4943,16 @@
       <c r="C8" s="28">
         <v>45904</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="52">
         <v>134151508</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="53">
         <v>3450065872</v>
       </c>
-      <c r="F8" s="55" t="s">
+      <c r="F8" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="G8" s="63" t="s">
+      <c r="G8" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H8" s="9" t="s">
@@ -4815,16 +4972,16 @@
       <c r="C9" s="28">
         <v>45904</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="52">
         <v>134151675</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="53">
         <v>3450065938</v>
       </c>
-      <c r="F9" s="55" t="s">
+      <c r="F9" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="G9" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H9" s="9" t="s">
@@ -4844,19 +5001,19 @@
       <c r="C10" s="28">
         <v>45904</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="52">
         <v>134156726</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="53">
         <v>3450066180</v>
       </c>
-      <c r="F10" s="55" t="s">
+      <c r="F10" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="60" t="s">
+      <c r="H10" s="9" t="s">
         <v>138</v>
       </c>
       <c r="I10" s="27">
@@ -4873,16 +5030,16 @@
       <c r="C11" s="28">
         <v>45904</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="52">
         <v>134151502</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="53">
         <v>3450065861</v>
       </c>
-      <c r="F11" s="56" t="s">
+      <c r="F11" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G11" s="63" t="s">
+      <c r="G11" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -4902,16 +5059,16 @@
       <c r="C12" s="28">
         <v>45904</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="52">
         <v>134160229</v>
       </c>
-      <c r="E12" s="59">
+      <c r="E12" s="53">
         <v>3450062946</v>
       </c>
-      <c r="F12" s="55" t="s">
+      <c r="F12" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G12" s="63" t="s">
+      <c r="G12" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H12" s="9" t="s">
@@ -4931,16 +5088,16 @@
       <c r="C13" s="28">
         <v>45904</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="52">
         <v>134142314</v>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="53">
         <v>3450065179</v>
       </c>
-      <c r="F13" s="55" t="s">
+      <c r="F13" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="55" t="s">
         <v>40</v>
       </c>
       <c r="H13" s="9" t="s">
@@ -4960,26 +5117,26 @@
       <c r="C14" s="28">
         <v>45904</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="52">
         <v>134160191</v>
       </c>
-      <c r="E14" s="59">
+      <c r="E14" s="53">
         <v>3450062980</v>
       </c>
-      <c r="F14" s="55" t="s">
+      <c r="F14" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="60" t="s">
+      <c r="H14" s="9" t="s">
         <v>142</v>
       </c>
       <c r="I14" s="27">
         <v>45894</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="61" customFormat="1">
+    <row r="15" spans="1:9">
       <c r="A15" s="29" t="s">
         <v>9</v>
       </c>
@@ -4989,19 +5146,19 @@
       <c r="C15" s="28">
         <v>45904</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="25">
         <v>134160582</v>
       </c>
       <c r="E15" s="18">
         <v>3450064783</v>
       </c>
-      <c r="F15" s="55" t="s">
+      <c r="F15" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="60" t="s">
+      <c r="H15" s="9" t="s">
         <v>144</v>
       </c>
       <c r="I15" s="27">
@@ -5018,19 +5175,19 @@
       <c r="C16" s="28">
         <v>45904</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="52">
         <v>134158678</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="53">
         <v>3450061824</v>
       </c>
-      <c r="F16" s="56" t="s">
+      <c r="F16" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="60" t="s">
+      <c r="H16" s="9" t="s">
         <v>146</v>
       </c>
       <c r="I16" s="27">
@@ -5047,16 +5204,16 @@
       <c r="C17" s="28">
         <v>45904</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="52">
         <v>134159195</v>
       </c>
-      <c r="E17" s="59">
+      <c r="E17" s="53">
         <v>3450066301</v>
       </c>
-      <c r="F17" s="56" t="s">
+      <c r="F17" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -5076,19 +5233,19 @@
       <c r="C18" s="28">
         <v>45904</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="52">
         <v>134195795</v>
       </c>
-      <c r="E18" s="59">
+      <c r="E18" s="53">
         <v>3450068138</v>
       </c>
-      <c r="F18" s="56" t="s">
+      <c r="F18" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="60" t="s">
+      <c r="H18" s="9" t="s">
         <v>149</v>
       </c>
       <c r="I18" s="27">
@@ -5105,16 +5262,16 @@
       <c r="C19" s="28">
         <v>45904</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="52">
         <v>134131938</v>
       </c>
-      <c r="E19" s="59">
+      <c r="E19" s="53">
         <v>3450064740</v>
       </c>
-      <c r="F19" s="55" t="s">
+      <c r="F19" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="9" t="s">
@@ -5134,16 +5291,16 @@
       <c r="C20" s="28">
         <v>45904</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="52">
         <v>134151203</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="53">
         <v>3450065817</v>
       </c>
-      <c r="F20" s="56" t="s">
+      <c r="F20" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -5163,19 +5320,19 @@
       <c r="C21" s="28">
         <v>45904</v>
       </c>
-      <c r="D21" s="58">
+      <c r="D21" s="52">
         <v>134181258</v>
       </c>
-      <c r="E21" s="59">
+      <c r="E21" s="53">
         <v>3450067511</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G21" s="64" t="s">
+      <c r="G21" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="60" t="s">
+      <c r="H21" s="9" t="s">
         <v>153</v>
       </c>
       <c r="I21" s="27">
@@ -5192,16 +5349,16 @@
       <c r="C22" s="28">
         <v>45904</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="52">
         <v>134158894</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="53">
         <v>3450066268</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H22" s="9" t="s">
@@ -5221,19 +5378,19 @@
       <c r="C23" s="28">
         <v>45904</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="52">
         <v>134272282</v>
       </c>
-      <c r="E23" s="59">
+      <c r="E23" s="53">
         <v>3450072428</v>
       </c>
-      <c r="F23" s="55" t="s">
+      <c r="F23" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="60" t="s">
+      <c r="H23" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="27">
@@ -5250,19 +5407,19 @@
       <c r="C24" s="28">
         <v>45904</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D24" s="52">
         <v>134073511</v>
       </c>
-      <c r="E24" s="59">
+      <c r="E24" s="53">
         <v>3450061329</v>
       </c>
-      <c r="F24" s="55" t="s">
+      <c r="F24" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G24" s="64" t="s">
+      <c r="G24" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="60" t="s">
+      <c r="H24" s="9" t="s">
         <v>157</v>
       </c>
       <c r="I24" s="27">
@@ -5279,19 +5436,19 @@
       <c r="C25" s="28">
         <v>45904</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="52">
         <v>134117765</v>
       </c>
-      <c r="E25" s="59">
+      <c r="E25" s="53">
         <v>3450063639</v>
       </c>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="60" t="s">
+      <c r="H25" s="9" t="s">
         <v>159</v>
       </c>
       <c r="I25" s="27">
@@ -5308,16 +5465,16 @@
       <c r="C26" s="28">
         <v>45904</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D26" s="52">
         <v>134119034</v>
       </c>
-      <c r="E26" s="59">
+      <c r="E26" s="53">
         <v>3450063727</v>
       </c>
-      <c r="F26" s="55" t="s">
+      <c r="F26" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H26" s="9" t="s">
@@ -5337,16 +5494,16 @@
       <c r="C27" s="28">
         <v>45904</v>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="52">
         <v>134119881</v>
       </c>
-      <c r="E27" s="59">
+      <c r="E27" s="53">
         <v>3450063782</v>
       </c>
-      <c r="F27" s="56" t="s">
+      <c r="F27" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="64" t="s">
+      <c r="G27" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H27" s="9" t="s">
@@ -5366,16 +5523,16 @@
       <c r="C28" s="28">
         <v>45904</v>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="52">
         <v>134123847</v>
       </c>
-      <c r="E28" s="59">
+      <c r="E28" s="53">
         <v>3450064156</v>
       </c>
-      <c r="F28" s="55" t="s">
+      <c r="F28" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H28" s="9" t="s">
@@ -5395,16 +5552,16 @@
       <c r="C29" s="28">
         <v>45904</v>
       </c>
-      <c r="D29" s="58">
+      <c r="D29" s="52">
         <v>134125124</v>
       </c>
-      <c r="E29" s="59">
+      <c r="E29" s="53">
         <v>3450064233</v>
       </c>
-      <c r="F29" s="56" t="s">
+      <c r="F29" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G29" s="64" t="s">
+      <c r="G29" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="9" t="s">
@@ -5424,16 +5581,16 @@
       <c r="C30" s="28">
         <v>45904</v>
       </c>
-      <c r="D30" s="58">
+      <c r="D30" s="52">
         <v>134125486</v>
       </c>
-      <c r="E30" s="59">
+      <c r="E30" s="53">
         <v>3450064255</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="G30" s="64" t="s">
+      <c r="G30" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H30" s="9" t="s">
@@ -5453,16 +5610,16 @@
       <c r="C31" s="28">
         <v>45904</v>
       </c>
-      <c r="D31" s="58">
+      <c r="D31" s="52">
         <v>134130794</v>
       </c>
-      <c r="E31" s="59">
+      <c r="E31" s="53">
         <v>3450064651</v>
       </c>
-      <c r="F31" s="56" t="s">
+      <c r="F31" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H31" s="9" t="s">
@@ -5482,16 +5639,16 @@
       <c r="C32" s="28">
         <v>45904</v>
       </c>
-      <c r="D32" s="58">
+      <c r="D32" s="52">
         <v>134131237</v>
       </c>
-      <c r="E32" s="59">
+      <c r="E32" s="53">
         <v>3450064684</v>
       </c>
-      <c r="F32" s="55" t="s">
+      <c r="F32" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H32" s="9" t="s">
@@ -5511,16 +5668,16 @@
       <c r="C33" s="28">
         <v>45904</v>
       </c>
-      <c r="D33" s="58">
+      <c r="D33" s="52">
         <v>134133609</v>
       </c>
-      <c r="E33" s="59">
+      <c r="E33" s="53">
         <v>3450064893</v>
       </c>
-      <c r="F33" s="55" t="s">
+      <c r="F33" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="64" t="s">
+      <c r="G33" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H33" s="9" t="s">
@@ -5540,16 +5697,16 @@
       <c r="C34" s="28">
         <v>45904</v>
       </c>
-      <c r="D34" s="58">
+      <c r="D34" s="52">
         <v>134134215</v>
       </c>
-      <c r="E34" s="59">
+      <c r="E34" s="53">
         <v>3450064960</v>
       </c>
-      <c r="F34" s="56" t="s">
+      <c r="F34" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="G34" s="64" t="s">
+      <c r="G34" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H34" s="9" t="s">
@@ -5569,16 +5726,16 @@
       <c r="C35" s="28">
         <v>45904</v>
       </c>
-      <c r="D35" s="58">
+      <c r="D35" s="52">
         <v>134134268</v>
       </c>
-      <c r="E35" s="59">
+      <c r="E35" s="53">
         <v>3450064970</v>
       </c>
-      <c r="F35" s="56" t="s">
+      <c r="F35" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H35" s="9" t="s">
@@ -5598,19 +5755,19 @@
       <c r="C36" s="28">
         <v>45904</v>
       </c>
-      <c r="D36" s="58">
+      <c r="D36" s="52">
         <v>134071048</v>
       </c>
-      <c r="E36" s="59">
+      <c r="E36" s="53">
         <v>3450061109</v>
       </c>
-      <c r="F36" s="56" t="s">
+      <c r="F36" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G36" s="64" t="s">
+      <c r="G36" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H36" s="60" t="s">
+      <c r="H36" s="9" t="s">
         <v>115</v>
       </c>
       <c r="I36" s="27">
@@ -5627,19 +5784,19 @@
       <c r="C37" s="28">
         <v>45904</v>
       </c>
-      <c r="D37" s="58">
+      <c r="D37" s="52">
         <v>134077361</v>
       </c>
-      <c r="E37" s="59">
+      <c r="E37" s="53">
         <v>3450061472</v>
       </c>
-      <c r="F37" s="56" t="s">
+      <c r="F37" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="G37" s="64" t="s">
+      <c r="G37" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="60" t="s">
+      <c r="H37" s="9" t="s">
         <v>172</v>
       </c>
       <c r="I37" s="27">
@@ -5656,19 +5813,19 @@
       <c r="C38" s="28">
         <v>45904</v>
       </c>
-      <c r="D38" s="58">
+      <c r="D38" s="52">
         <v>134077137</v>
       </c>
-      <c r="E38" s="59">
+      <c r="E38" s="53">
         <v>3450061461</v>
       </c>
-      <c r="F38" s="55" t="s">
+      <c r="F38" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="G38" s="64" t="s">
+      <c r="G38" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="60" t="s">
+      <c r="H38" s="9" t="s">
         <v>174</v>
       </c>
       <c r="I38" s="27">
@@ -5685,19 +5842,19 @@
       <c r="C39" s="28">
         <v>45904</v>
       </c>
-      <c r="D39" s="58">
+      <c r="D39" s="52">
         <v>134285315</v>
       </c>
-      <c r="E39" s="59">
+      <c r="E39" s="53">
         <v>3450070360</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="G39" s="64" t="s">
+      <c r="G39" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="60" t="s">
+      <c r="H39" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="27">
@@ -5714,16 +5871,16 @@
       <c r="C40" s="28">
         <v>45904</v>
       </c>
-      <c r="D40" s="58">
+      <c r="D40" s="52">
         <v>134139465</v>
       </c>
-      <c r="E40" s="59">
+      <c r="E40" s="53">
         <v>3450065091</v>
       </c>
-      <c r="F40" s="55" t="s">
+      <c r="F40" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="G40" s="64" t="s">
+      <c r="G40" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H40" s="9" t="s">
@@ -5743,16 +5900,16 @@
       <c r="C41" s="28">
         <v>45904</v>
       </c>
-      <c r="D41" s="58">
+      <c r="D41" s="52">
         <v>134144563</v>
       </c>
-      <c r="E41" s="59">
+      <c r="E41" s="53">
         <v>3450065256</v>
       </c>
-      <c r="F41" s="56" t="s">
+      <c r="F41" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H41" s="9" t="s">
@@ -5772,16 +5929,16 @@
       <c r="C42" s="28">
         <v>45904</v>
       </c>
-      <c r="D42" s="58">
+      <c r="D42" s="52">
         <v>134146490</v>
       </c>
-      <c r="E42" s="59">
+      <c r="E42" s="53">
         <v>3450065410</v>
       </c>
-      <c r="F42" s="56" t="s">
+      <c r="F42" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G42" s="64" t="s">
+      <c r="G42" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H42" s="9" t="s">
@@ -5801,16 +5958,16 @@
       <c r="C43" s="28">
         <v>45904</v>
       </c>
-      <c r="D43" s="58">
+      <c r="D43" s="52">
         <v>134146948</v>
       </c>
-      <c r="E43" s="59">
+      <c r="E43" s="53">
         <v>3450065465</v>
       </c>
-      <c r="F43" s="55" t="s">
+      <c r="F43" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H43" s="9" t="s">
@@ -5830,16 +5987,16 @@
       <c r="C44" s="28">
         <v>45904</v>
       </c>
-      <c r="D44" s="58">
+      <c r="D44" s="52">
         <v>134151477</v>
       </c>
-      <c r="E44" s="59">
+      <c r="E44" s="53">
         <v>3450065840</v>
       </c>
-      <c r="F44" s="56" t="s">
+      <c r="F44" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="G44" s="64" t="s">
+      <c r="G44" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H44" s="9" t="s">
@@ -5859,16 +6016,16 @@
       <c r="C45" s="28">
         <v>45904</v>
       </c>
-      <c r="D45" s="58">
+      <c r="D45" s="52">
         <v>134151955</v>
       </c>
-      <c r="E45" s="59">
+      <c r="E45" s="53">
         <v>3450065950</v>
       </c>
-      <c r="F45" s="55" t="s">
+      <c r="F45" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H45" s="9" t="s">
@@ -5888,16 +6045,16 @@
       <c r="C46" s="28">
         <v>45904</v>
       </c>
-      <c r="D46" s="58">
+      <c r="D46" s="52">
         <v>134154522</v>
       </c>
-      <c r="E46" s="59">
+      <c r="E46" s="53">
         <v>3450066059</v>
       </c>
-      <c r="F46" s="55" t="s">
+      <c r="F46" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="G46" s="64" t="s">
+      <c r="G46" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H46" s="9" t="s">
@@ -5917,19 +6074,19 @@
       <c r="C47" s="28">
         <v>45904</v>
       </c>
-      <c r="D47" s="58">
+      <c r="D47" s="52">
         <v>134084614</v>
       </c>
-      <c r="E47" s="59">
+      <c r="E47" s="53">
         <v>3450062011</v>
       </c>
-      <c r="F47" s="55" t="s">
+      <c r="F47" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="60" t="s">
+      <c r="H47" s="9" t="s">
         <v>172</v>
       </c>
       <c r="I47" s="27">
@@ -5946,16 +6103,16 @@
       <c r="C48" s="28">
         <v>45904</v>
       </c>
-      <c r="D48" s="58">
+      <c r="D48" s="52">
         <v>134156516</v>
       </c>
-      <c r="E48" s="59">
+      <c r="E48" s="53">
         <v>3450062088</v>
       </c>
-      <c r="F48" s="56" t="s">
+      <c r="F48" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="G48" s="64" t="s">
+      <c r="G48" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H48" s="9" t="s">
@@ -5975,16 +6132,16 @@
       <c r="C49" s="28">
         <v>45904</v>
       </c>
-      <c r="D49" s="58">
+      <c r="D49" s="52">
         <v>134156704</v>
       </c>
-      <c r="E49" s="59">
+      <c r="E49" s="53">
         <v>3450062055</v>
       </c>
-      <c r="F49" s="56" t="s">
+      <c r="F49" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="64" t="s">
+      <c r="G49" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H49" s="9" t="s">
@@ -6004,16 +6161,16 @@
       <c r="C50" s="28">
         <v>45904</v>
       </c>
-      <c r="D50" s="58">
+      <c r="D50" s="52">
         <v>134157147</v>
       </c>
-      <c r="E50" s="59">
+      <c r="E50" s="53">
         <v>3450066191</v>
       </c>
-      <c r="F50" s="55" t="s">
+      <c r="F50" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="G50" s="64" t="s">
+      <c r="G50" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H50" s="9" t="s">
@@ -6033,16 +6190,16 @@
       <c r="C51" s="28">
         <v>45904</v>
       </c>
-      <c r="D51" s="58">
+      <c r="D51" s="52">
         <v>134158807</v>
       </c>
-      <c r="E51" s="59">
+      <c r="E51" s="53">
         <v>3450061747</v>
       </c>
-      <c r="F51" s="56" t="s">
+      <c r="F51" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="64" t="s">
+      <c r="G51" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H51" s="9" t="s">
@@ -6062,16 +6219,16 @@
       <c r="C52" s="28">
         <v>45904</v>
       </c>
-      <c r="D52" s="58">
+      <c r="D52" s="52">
         <v>134158935</v>
       </c>
-      <c r="E52" s="59">
+      <c r="E52" s="53">
         <v>3450061527</v>
       </c>
-      <c r="F52" s="56" t="s">
+      <c r="F52" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="G52" s="64" t="s">
+      <c r="G52" s="56" t="s">
         <v>40</v>
       </c>
       <c r="H52" s="9" t="s">
@@ -6091,19 +6248,19 @@
       <c r="C53" s="28">
         <v>45904</v>
       </c>
-      <c r="D53" s="58">
+      <c r="D53" s="52">
         <v>134162394</v>
       </c>
-      <c r="E53" s="59">
+      <c r="E53" s="53">
         <v>3450066323</v>
       </c>
-      <c r="F53" s="55" t="s">
+      <c r="F53" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="G53" s="64" t="s">
+      <c r="G53" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H53" s="60" t="s">
+      <c r="H53" s="9" t="s">
         <v>190</v>
       </c>
       <c r="I53" s="27">
@@ -6120,19 +6277,19 @@
       <c r="C54" s="28">
         <v>45904</v>
       </c>
-      <c r="D54" s="58">
+      <c r="D54" s="52">
         <v>134199244</v>
       </c>
-      <c r="E54" s="59">
+      <c r="E54" s="53">
         <v>3450068370</v>
       </c>
-      <c r="F54" s="56" t="s">
+      <c r="F54" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="G54" s="64" t="s">
+      <c r="G54" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H54" s="60" t="s">
+      <c r="H54" s="9" t="s">
         <v>192</v>
       </c>
       <c r="I54" s="27">
@@ -6163,10 +6320,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" customWidth="1"/>
@@ -6195,7 +6352,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6206,384 +6363,908 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45893</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D2" s="52">
+        <v>134091381</v>
+      </c>
+      <c r="E2" s="61">
+        <v>3450062220</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45904</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D3" s="52">
+        <v>134170741</v>
+      </c>
+      <c r="E3" s="61">
+        <v>3450065894</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D4" s="52">
+        <v>134161553</v>
+      </c>
+      <c r="E4" s="61">
+        <v>3450064563</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D5" s="52">
+        <v>134171037</v>
+      </c>
+      <c r="E5" s="61">
+        <v>3450066796</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D6" s="52">
+        <v>134180317</v>
+      </c>
+      <c r="E6" s="61">
+        <v>3450067434</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D7" s="52">
+        <v>134184079</v>
+      </c>
+      <c r="E7" s="61">
+        <v>3450067654</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D8" s="52">
+        <v>134178123</v>
+      </c>
+      <c r="E8" s="61">
+        <v>3450067236</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D9" s="52">
+        <v>134165952</v>
+      </c>
+      <c r="E9" s="61">
+        <v>3450066499</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D10" s="52">
+        <v>134167202</v>
+      </c>
+      <c r="E10" s="61">
+        <v>3450066565</v>
+      </c>
+      <c r="F10" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D11" s="52">
+        <v>134213558</v>
+      </c>
+      <c r="E11" s="61">
+        <v>3450069106</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="64" t="s">
+        <v>204</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45904</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D12" s="52">
+        <v>134230438</v>
+      </c>
+      <c r="E12" s="61">
+        <v>3450070130</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="64" t="s">
+        <v>206</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45905</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45902</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D13" s="52">
+        <v>134247248</v>
+      </c>
+      <c r="E13" s="61">
+        <v>3450070877</v>
+      </c>
+      <c r="F13" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45904</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D14" s="52">
+        <v>134270150</v>
+      </c>
+      <c r="E14" s="61">
+        <v>3450072197</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="64" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45909</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D15" s="52">
+        <v>134264217</v>
+      </c>
+      <c r="E15" s="61">
+        <v>3450071790</v>
+      </c>
+      <c r="F15" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="64" t="s">
+        <v>204</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45904</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="7">
+        <v>45904</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D16" s="52">
+        <v>134288985</v>
+      </c>
+      <c r="E16" s="61">
+        <v>3450073154</v>
+      </c>
+      <c r="F16" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45904</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D17" s="52">
+        <v>134184515</v>
+      </c>
+      <c r="E17" s="61">
+        <v>3450067676</v>
+      </c>
+      <c r="F17" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="27"/>
+      <c r="B18" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D18" s="52">
+        <v>134133617</v>
+      </c>
+      <c r="E18" s="61">
+        <v>3450064904</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>212</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45905</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D19" s="52">
+        <v>134169949</v>
+      </c>
+      <c r="E19" s="58">
+        <v>3450066664</v>
+      </c>
+      <c r="F19" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="G19" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45905</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D20" s="52">
+        <v>134161572</v>
+      </c>
+      <c r="E20" s="48">
+        <v>3450063771</v>
+      </c>
+      <c r="F20" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D21" s="52">
+        <v>134169958</v>
+      </c>
+      <c r="E21" s="48">
+        <v>3450066675</v>
+      </c>
+      <c r="F21" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="G21" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D22" s="52">
+        <v>134161577</v>
+      </c>
+      <c r="E22" s="48">
+        <v>3450063749</v>
+      </c>
+      <c r="F22" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D23" s="52">
+        <v>134169561</v>
+      </c>
+      <c r="E23" s="48">
+        <v>3450066158</v>
+      </c>
+      <c r="F23" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="G23" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D24" s="52">
+        <v>134165135</v>
+      </c>
+      <c r="E24" s="48">
+        <v>3450066444</v>
+      </c>
+      <c r="F24" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D25" s="52">
+        <v>134167349</v>
+      </c>
+      <c r="E25" s="48">
+        <v>3450066576</v>
+      </c>
+      <c r="F25" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D26" s="52">
+        <v>134171657</v>
+      </c>
+      <c r="E26" s="48">
+        <v>3450066830</v>
+      </c>
+      <c r="F26" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D27" s="52">
+        <v>134173263</v>
+      </c>
+      <c r="E27" s="48">
+        <v>3450066939</v>
+      </c>
+      <c r="F27" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D28" s="52">
+        <v>134175866</v>
+      </c>
+      <c r="E28" s="48">
+        <v>3450067104</v>
+      </c>
+      <c r="F28" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D29" s="52">
+        <v>134178173</v>
+      </c>
+      <c r="E29" s="48">
+        <v>3450067258</v>
+      </c>
+      <c r="F29" s="59" t="s">
+        <v>225</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="27"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D30" s="52">
+        <v>134178347</v>
+      </c>
+      <c r="E30" s="48">
+        <v>3450067269</v>
+      </c>
+      <c r="F30" s="59" t="s">
+        <v>226</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="27"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D31" s="52">
+        <v>134179577</v>
+      </c>
+      <c r="E31" s="48">
+        <v>3450067379</v>
+      </c>
+      <c r="F31" s="59" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="27"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C32" s="28">
+        <v>45905</v>
+      </c>
+      <c r="D32" s="52">
+        <v>134181932</v>
+      </c>
+      <c r="E32" s="48">
+        <v>3450067555</v>
+      </c>
+      <c r="F32" s="60" t="s">
+        <v>228</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="15"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="I33" s="27"/>
@@ -6592,7 +7273,7 @@
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
@@ -6832,12 +7513,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
@@ -6850,7 +7531,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -6896,72 +7577,154 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45906</v>
+      </c>
+      <c r="D2" s="57">
+        <v>134120789</v>
+      </c>
+      <c r="E2" s="47">
+        <v>3450063870</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="62" t="s">
+        <v>230</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="36"/>
+      <c r="B3" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45906</v>
+      </c>
+      <c r="D3" s="25">
+        <v>134258691</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450071394</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45906</v>
+      </c>
+      <c r="D4" s="25">
+        <v>134127370</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450064354</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45895</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45906</v>
+      </c>
+      <c r="D5" s="25">
+        <v>134134592</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450064992</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45906</v>
+      </c>
+      <c r="D6" s="25">
+        <v>134192707</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450067918</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="6"/>
       <c r="H7" s="9"/>
       <c r="I7" s="11"/>
@@ -7001,66 +7764,61 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="7"/>
       <c r="D11" s="8"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="6"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="6"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="7"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
     </row>
@@ -7070,7 +7828,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
     </row>
@@ -7374,67 +8132,17 @@
       <c r="G47" s="6"/>
       <c r="H47" s="9"/>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A10" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -8107,6 +8815,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496573</_dlc_DocId>
@@ -8149,7 +8916,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8527,77 +9294,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3965E57E-4F4E-44C0-B021-D89F8EC97D7C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>